--- a/314e-ig/output/StructureDefinition-observation-microbiology-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-observation-microbiology-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T12:06:33+05:30</t>
+    <t>2026-05-26T19:54:55+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-observation-microbiology-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-observation-microbiology-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T19:54:55+05:30</t>
+    <t>2026-06-10T16:33:40+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -633,7 +633,7 @@
     <t>valueAttachment</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://314e.com/fhir/ig/StructureDefinition/value-attachment-314e}
+    <t xml:space="preserve">Extension {http://314e.com/fhir/StructureDefinition/observation-valueAttachment}
 </t>
   </si>
   <si>

--- a/314e-ig/output/StructureDefinition-observation-microbiology-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-observation-microbiology-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T16:33:40+05:30</t>
+    <t>2026-06-11T14:17:09+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -322,7 +322,7 @@
     <t>Observation.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">Meta
+    <t xml:space="preserve">Meta {http://314e.com/fhir/StructureDefinition/meta-314e}
 </t>
   </si>
   <si>

--- a/314e-ig/output/StructureDefinition-observation-microbiology-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-observation-microbiology-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:17:09+05:30</t>
+    <t>2026-06-18T13:36:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-observation-microbiology-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-observation-microbiology-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:36:33+05:30</t>
+    <t>2026-06-18T14:15:04+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-observation-microbiology-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-observation-microbiology-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:15:04+05:30</t>
+    <t>2026-06-18T16:14:31+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-observation-microbiology-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-observation-microbiology-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T16:14:31+05:30</t>
+    <t>2026-06-24T16:34:23+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -920,7 +920,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|DeviceRequest|ImmunizationRecommendation|MedicationRequest|NutritionOrder|ServiceRequest) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/servicerequest-314e|http://314e.com/fhir/StructureDefinition/careplan-314e|http://314e.com/fhir/StructureDefinition/devicerequest-314e|http://314e.com/fhir/StructureDefinition/immunizationrecommendation-314e|http://314e.com/fhir/StructureDefinition/medicationrequest-314e|http://314e.com/fhir/StructureDefinition/nutritionorder-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -949,7 +949,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Immunization|ImagingStudy) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/medicationadministration-314e|http://314e.com/fhir/StructureDefinition/medicationdispense-314e|MedicationStatement|http://314e.com/fhir/StructureDefinition/procedure-314e|http://314e.com/fhir/StructureDefinition/immunization-314e|http://314e.com/fhir/StructureDefinition/imagingstudy-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1127,7 +1127,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-patient) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/patient-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1158,7 +1158,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(Resource|http://314e.com/fhir/StructureDefinition/account-314e|http://314e.com/fhir/StructureDefinition/allergyintolerance-314e|http://314e.com/fhir/StructureDefinition/appointment-314e|http://314e.com/fhir/StructureDefinition/careplan-314e|http://314e.com/fhir/StructureDefinition/careteam-314e|http://314e.com/fhir/StructureDefinition/clinicalimpression-314e|http://314e.com/fhir/StructureDefinition/communicationrequest-314e|http://314e.com/fhir/StructureDefinition/condition-314e|http://314e.com/fhir/StructureDefinition/condition-diagnosis-314e|http://314e.com/fhir/StructureDefinition/condition-problem-healthconcern-314e|http://314e.com/fhir/StructureDefinition/contract-314e|http://314e.com/fhir/StructureDefinition/coverage-314e|http://314e.com/fhir/StructureDefinition/detectedissue-314e|http://314e.com/fhir/StructureDefinition/device-314e|http://314e.com/fhir/StructureDefinition/devicerequest-314e|http://314e.com/fhir/StructureDefinition/diagnosticreport-314e|http://314e.com/fhir/StructureDefinition/diagnosticreport-lab-314e|http://314e.com/fhir/StructureDefinition/diagnosticreport-notereport-314e|http://314e.com/fhir/StructureDefinition/documentreference-314e|http://314e.com/fhir/StructureDefinition/encounter-314e|http://314e.com/fhir/StructureDefinition/endpoint-314e|http://314e.com/fhir/StructureDefinition/episodeofcare-314e|http://314e.com/fhir/StructureDefinition/goal-314e|http://314e.com/fhir/StructureDefinition/group-314e|http://314e.com/fhir/StructureDefinition/healthcareservice-314e|http://314e.com/fhir/StructureDefinition/imagingstudy-314e|http://314e.com/fhir/StructureDefinition/immunization-314e|http://314e.com/fhir/StructureDefinition/immunizationevaluation-314e|http://314e.com/fhir/StructureDefinition/immunizationrecommendation-314e|http://314e.com/fhir/StructureDefinition/location-314e|http://314e.com/fhir/StructureDefinition/media-314e|http://314e.com/fhir/StructureDefinition/medication-314e|http://314e.com/fhir/StructureDefinition/medicationadministration-314e|http://314e.com/fhir/StructureDefinition/medicationdispense-314e|http://314e.com/fhir/StructureDefinition/medicationrequest-314e|http://314e.com/fhir/StructureDefinition/molecularsequence-314e|http://314e.com/fhir/StructureDefinition/nutritionorder-314e|http://314e.com/fhir/StructureDefinition/observation-314e|http://314e.com/fhir/StructureDefinition/observation-antimicrobial-susceptibility-314e|http://314e.com/fhir/StructureDefinition/observation-lab-general-314e|http://314e.com/fhir/StructureDefinition/observation-microbiology-314e|http://314e.com/fhir/StructureDefinition/observation-microorganism-314e|http://314e.com/fhir/StructureDefinition/organization-314e|http://314e.com/fhir/StructureDefinition/patient-314e|http://314e.com/fhir/StructureDefinition/practitioner-314e|http://314e.com/fhir/StructureDefinition/practitionerrole-314e|http://314e.com/fhir/StructureDefinition/procedure-314e|http://314e.com/fhir/StructureDefinition/questionnaireresponse-314e|http://314e.com/fhir/StructureDefinition/relatedperson-314e|http://314e.com/fhir/StructureDefinition/requestgroup-314e|http://314e.com/fhir/StructureDefinition/schedule-314e|http://314e.com/fhir/StructureDefinition/servicerequest-314e|http://314e.com/fhir/StructureDefinition/slot-314e|http://314e.com/fhir/StructureDefinition/specimen-314e|http://314e.com/fhir/StructureDefinition/substance-314e|http://314e.com/fhir/StructureDefinition/task-314e|http://314e.com/fhir/StructureDefinition/visionprescription-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1181,7 +1181,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-encounter) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/encounter-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1280,7 +1280,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|Patient|RelatedPerson) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/practitioner-314e|http://314e.com/fhir/StructureDefinition/practitionerrole-314e|http://314e.com/fhir/StructureDefinition/organization-314e|http://314e.com/fhir/StructureDefinition/careteam-314e|http://314e.com/fhir/StructureDefinition/patient-314e|http://314e.com/fhir/StructureDefinition/relatedperson-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1500,7 +1500,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-specimen) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/specimen-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1528,7 +1528,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/device-314e|DeviceMetric) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1764,7 +1764,7 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|Media|QuestionnaireResponse|Observation|MolecularSequence) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/documentreference-314e|http://314e.com/fhir/StructureDefinition/imagingstudy-314e|http://314e.com/fhir/StructureDefinition/media-314e|http://314e.com/fhir/StructureDefinition/questionnaireresponse-314e|http://314e.com/fhir/StructureDefinition/observation-314e|http://314e.com/fhir/StructureDefinition/observation-lab-general-314e|http://314e.com/fhir/StructureDefinition/observation-microbiology-314e|http://314e.com/fhir/StructureDefinition/observation-microorganism-314e|http://314e.com/fhir/StructureDefinition/observation-antimicrobial-susceptibility-314e|http://314e.com/fhir/StructureDefinition/molecularsequence-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>

--- a/314e-ig/output/StructureDefinition-observation-microbiology-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-observation-microbiology-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T16:34:23+05:30</t>
+    <t>2026-06-29T17:18:47+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-observation-microbiology-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-observation-microbiology-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:18:47+05:30</t>
+    <t>2026-07-01T18:18:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
